--- a/data/passenger_time_value.xlsx
+++ b/data/passenger_time_value.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ADF6EF-7EA3-42A7-A850-22AB48FF5CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB35D5D-4602-4070-A521-144D05DB0F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -439,7 +439,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>22.34</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -447,7 +447,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>54.56</v>
+        <v>55.9</v>
       </c>
     </row>
   </sheetData>
@@ -476,7 +476,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>68.400000000000006</v>
+        <v>69.099999999999994</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -484,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>70</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>95.5</v>
+        <v>96.4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -500,7 +500,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>71.099999999999994</v>
+        <v>71.8</v>
       </c>
     </row>
   </sheetData>
@@ -526,7 +526,7 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -534,7 +534,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>76.7</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -542,7 +542,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>72.900000000000006</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
   </sheetData>
@@ -568,7 +568,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>50.3</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -576,7 +576,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>88.1</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -584,7 +584,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>65.599999999999994</v>
+        <v>72.3</v>
       </c>
     </row>
   </sheetData>
@@ -593,9 +593,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -822,27 +825,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0278CDF3-8D6A-4741-AAC3-7F274BAD8D3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62A5CA49-98BE-41B8-A8DB-86FD21BF1081}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -867,9 +858,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62A5CA49-98BE-41B8-A8DB-86FD21BF1081}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0278CDF3-8D6A-4741-AAC3-7F274BAD8D3A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
